--- a/hira_material_automation/output/monthly/202601_202604__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__all_suture_anchor__040021__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:23</t>
+          <t>2026-04-14T21:55:23</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c8c2497fa659e76a7d12fda94f38b419e4b4f292774996ddd8fafc6306e7d9e4</t>
+          <t>3a562cfce23d33d51ca0113efb86b42f578ec208daad23cf78718be3ab9f4cad</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__all_suture_anchor__040021__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:23</t>
+          <t>2026-04-24T21:52:59</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3a562cfce23d33d51ca0113efb86b42f578ec208daad23cf78718be3ab9f4cad</t>
+          <t>b8593ff5c17bf58464b23a2baeed7d78f59fb53766094658271a5a9b3d52055f</t>
         </is>
       </c>
     </row>
